--- a/salidas/resumen_universo.xlsx
+++ b/salidas/resumen_universo.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,117 +429,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Ticker Yahoo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Empresa (universo)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Años en el top 100</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Número de años</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Mejor rank</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Estado de selección</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fuente del universo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Empresa según SEC</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CIK</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>CIK anteriores usados</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Splits aplicados</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Tag EPS usado</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Tag acciones usado</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Meses con precio</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Rango precio</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Meses con P/E</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Rango P/E</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Meses con market cap</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Rango market cap</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Error Yahoo</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Error SEC EDGAR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Error P/E - market cap</t>
         </is>
@@ -5816,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="F60" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5907,7 +5919,7 @@
         <v>5</v>
       </c>
       <c r="F61" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5998,7 +6010,7 @@
         <v>8</v>
       </c>
       <c r="F62" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6271,7 +6283,7 @@
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -6453,7 +6465,7 @@
         <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -6988,11 +7000,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2010, 2015, 2017</t>
+          <t>2010, 2015, 2016, 2017</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73" t="n">
         <v>87</v>
@@ -7537,7 +7549,7 @@
         <v>2</v>
       </c>
       <c r="F79" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9072,7 +9084,7 @@
         <v>5</v>
       </c>
       <c r="F96" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -12088,7 +12100,7 @@
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2000-06-27 2:1; 2001-09-12 2:1; 2006-04-07 2:1; 2007-09-11 1.5:1; 2021-07-20 4:1; 2024-06-10 10:1</t>
+          <t>2000-06-27 2:1; 2001-09-10 2:1; 2006-04-07 2:1; 2007-09-11 1.5:1; 2021-07-20 4:1; 2024-06-10 10:1</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -15750,7 +15762,7 @@
         <v>11</v>
       </c>
       <c r="F170" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -16224,7 +16236,11 @@
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>1997-06-04 2:1; 2025-02-24 1.323:1</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>calculado: NetIncomeLoss / WeightedAverageNumberOfDilutedSharesOutstanding, us-gaap:EarningsPerShareDiluted</t>
@@ -16311,7 +16327,11 @@
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>1985-09-04 1.5:1</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted</t>
@@ -16398,7 +16418,11 @@
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>1977-06-20 2:1; 1988-07-01 1.5:1; 1989-07-24 2:1; 1993-06-29 2:1; 1997-10-14 2:1; 2006-08-14 2:1</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>us-gaap:EarningsPerShareDiluted</t>
@@ -16410,22 +16434,30 @@
         </is>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
-      </c>
-      <c r="P177" t="inlineStr"/>
+        <v>249</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>2006-01 a 2026-09</t>
+        </is>
+      </c>
       <c r="Q177" t="n">
-        <v>0</v>
-      </c>
-      <c r="R177" t="inlineStr"/>
+        <v>188</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>2011-02 a 2026-09</t>
+        </is>
+      </c>
       <c r="S177" t="n">
-        <v>0</v>
-      </c>
-      <c r="T177" t="inlineStr"/>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>Yahoo Finance regresó datos vacíos (ticker deslistado, renombrado o mal escrito)</t>
-        </is>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>2009-08 a 2026-09</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr"/>
       <c r="V177" t="inlineStr"/>
       <c r="W177" t="inlineStr"/>
     </row>
@@ -16559,7 +16591,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Exxon Mobil Corporation</t>
+          <t>ExxonMobil Holdings Corp</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
